--- a/Q3/non_linear_torque.xlsx
+++ b/Q3/non_linear_torque.xlsx
@@ -5,17 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/polatozturk/Desktop/EE568_Project_1/Q2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/polatozturk/Desktop/EE568_Project_1/Q3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B287250-B0B7-614F-AF96-47B8C2300166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB974EEF-DB46-8142-AE4E-2F2F68FFDE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="4540" yWindow="500" windowWidth="28800" windowHeight="16460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -55,15 +56,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Theta(rad)</t>
   </si>
   <si>
-    <t>FEA Torque(Nm)</t>
+    <t>Analytical Torque(Nm)</t>
   </si>
   <si>
-    <t>Analytical Torque(Nm)</t>
+    <t>Soft Iron FEA Torque(Nm)</t>
+  </si>
+  <si>
+    <t>M330-35A FEA Torque(Nm)</t>
   </si>
 </sst>
 </file>
@@ -133,6 +137,36 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Analytical and FEA Inductance vs. Theta</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-TR">
+              <a:effectLst/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -177,7 +211,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>FEA Torque(Nm)</c:v>
+                  <c:v>M330-35A FEA Torque(Nm)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -956,7 +990,1200 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800" b="0" i="0" baseline="0">
+                <a:effectLst/>
+              </a:rPr>
+              <a:t>Analytical and FEA Torque vs. Theta</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-TR">
+              <a:effectLst/>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-TR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>M330-35A FEA Torque(Nm)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.7266462599716474E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.17453292519943295</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.26179938779914941</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.3490658503988659</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.43633231299858238</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.52359877559829882</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.6108652381980153</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.69813170079773179</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.78539816339744828</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.87266462599716477</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.95993108859688125</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0471975511965976</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1344640137963142</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.2217304763960306</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.3089969389957472</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.3962634015954636</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.48352986419518</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.5707963267948966</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.6580627893946129</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.7453292519943295</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.8325957145940459</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.9198621771937625</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.0071286397934789</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.0943951023931953</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.1816615649929116</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.2689280275926285</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.3561944901923448</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.4434609527920612</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.5307274153917776</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.6179938779914944</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.7052603405912108</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.7925268031909272</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2.8797932657906435</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.9670597283903599</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3.0543261909900767</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3.1415926535897931</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>-3.13441502754021E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-4.3807297072863918E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-6.4216841199362579E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-5.9266647353117263E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-8.7825900689753683E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-7.4695507066749461E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-7.4249701527074149E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-9.1327974001579132E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-8.2850141788237436E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-8.3517871231144625E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-6.2128262670172928E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-7.2049984535188946E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-7.7880914041881008E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-7.670624092582673E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-5.9615004487133673E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-7.3792494393496305E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-3.2651458109158989E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-1.1206597362400577E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-9.172749778181094E-5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.1246334214242162E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.3082898974769286E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>7.5000851174903696E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.8796311269577961E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7.7524829829209774E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>7.4713664468502972E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>7.0922440480039886E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>6.2256025698402516E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>8.7969946248796463E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>8.2645424903713627E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9.6819840914275146E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>7.4518283162524068E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>6.8440002211803908E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>8.7044204309703055E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>5.8439421036561565E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>6.313820376079872E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>4.545719796837551E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-3.0631538692222211E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8F85-6948-B8D3-FE53350A8FF3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Analytical Torque(Nm)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.7266462599716474E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.17453292519943295</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.26179938779914941</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.3490658503988659</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.43633231299858238</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.52359877559829882</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.6108652381980153</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.69813170079773179</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.78539816339744828</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.87266462599716477</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.95993108859688125</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0471975511965976</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1344640137963142</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.2217304763960306</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.3089969389957472</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.3962634015954636</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.48352986419518</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.5707963267948966</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.6580627893946129</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.7453292519943295</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.8325957145940459</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.9198621771937625</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.0071286397934789</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.0943951023931953</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.1816615649929116</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.2689280275926285</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.3561944901923448</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.4434609527920612</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.5307274153917776</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.6179938779914944</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.7052603405912108</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.7925268031909272</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2.8797932657906435</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.9670597283903599</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3.0543261909900767</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3.1415926535897931</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$C$2:$C$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-1.7039227433567537E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-3.3560726563831238E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4.9062499999999988E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-6.3073534200491652E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-7.516811098104971E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-8.4978742746348035E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-9.2207338414617243E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-9.6634260764322896E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-9.812499999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-9.6634260764322896E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-9.2207338414617257E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-8.4978742746348035E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-7.516811098104971E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-6.3073534200491679E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-4.9062499999999988E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-3.3560726563831259E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-1.7039227433567575E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-1.2016846716633401E-17</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.7039227433567505E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.3560726563831231E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.9062499999999974E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>6.3073534200491652E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>7.5168110981049696E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>8.4978742746348007E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>9.2207338414617229E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9.6634260764322896E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>9.812499999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>9.663426076432291E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>9.2207338414617271E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>8.4978742746348035E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>7.5168110981049724E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6.3073534200491693E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4.9062500000000037E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3.3560726563831307E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1.7039227433567544E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2.4033693433266803E-17</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8F85-6948-B8D3-FE53350A8FF3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Soft Iron FEA Torque(Nm)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Sheet1!$A$2:$A$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.7266462599716474E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.17453292519943295</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.26179938779914941</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.3490658503988659</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.43633231299858238</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.52359877559829882</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.6108652381980153</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.69813170079773179</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.78539816339744828</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.87266462599716477</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.95993108859688125</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1.0471975511965976</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1.1344640137963142</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1.2217304763960306</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1.3089969389957472</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1.3962634015954636</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>1.48352986419518</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>1.5707963267948966</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.6580627893946129</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1.7453292519943295</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1.8325957145940459</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1.9198621771937625</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2.0071286397934789</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2.0943951023931953</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2.1816615649929116</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2.2689280275926285</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2.3561944901923448</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2.4434609527920612</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2.5307274153917776</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2.6179938779914944</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2.7052603405912108</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2.7925268031909272</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2.8797932657906435</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2.9670597283903599</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3.0543261909900767</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>3.1415926535897931</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Sheet1!$D$2:$D$38</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="37"/>
+                <c:pt idx="0">
+                  <c:v>-2.481354816340198E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-3.4170203009310077E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-5.0778897812623715E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-4.7698632003669188E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-7.1203673875896642E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-6.1565814782512031E-2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-6.1585023250091853E-2</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-7.6357111013341666E-2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-7.0242739037592747E-2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-7.2063441419449079E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-5.4431014025515964E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-6.3586025029903931E-2</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-6.9634672274783899E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-6.9121449390450146E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-5.4767270689186465E-2</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-6.7734174317896106E-2</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-3.036914355966126E-2</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-1.047889200553565E-2</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-8.6185038707664097E-5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1.0516091580590683E-2</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>3.0767640202002844E-2</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>6.8839772226522808E-2</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>5.3994415652076994E-2</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>6.9765887068951926E-2</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>6.6843584513800139E-2</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>6.2583274706921349E-2</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5.4549716300102309E-2</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>7.583773319791956E-2</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>7.0065438360958368E-2</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>8.0926870706645407E-2</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6.1786274525273813E-2</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>5.644731381453743E-2</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>7.0555798178302695E-2</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4.7012755730280992E-2</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.9902252679533167E-2</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>3.5444694990053066E-2</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-2.423451475907269E-4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8F85-6948-B8D3-FE53350A8FF3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="3577567"/>
+        <c:axId val="3579215"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="3577567"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-TR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="3579215"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="3579215"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-TR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="3577567"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-TR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-TR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -1512,20 +2739,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>184150</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>139700</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>82550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1545,6 +3288,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>374650</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>177800</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF404EB7-A519-9699-58F6-3A0DCF95202A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1850,25 +3629,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1879,8 +3661,11 @@
         <f t="array" ref="C2:C38">-(2.5^2)*0.0157*SIN(2*A2:A38)</f>
         <v>0</v>
       </c>
+      <c r="D2">
+        <v>-2.481354816340198E-4</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>8.7266462599716474E-2</v>
       </c>
@@ -1890,8 +3675,11 @@
       <c r="C3">
         <v>-1.7039227433567537E-2</v>
       </c>
+      <c r="D3">
+        <v>-3.4170203009310077E-2</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>0.17453292519943295</v>
       </c>
@@ -1901,8 +3689,11 @@
       <c r="C4">
         <v>-3.3560726563831238E-2</v>
       </c>
+      <c r="D4">
+        <v>-5.0778897812623715E-2</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>0.26179938779914941</v>
       </c>
@@ -1912,8 +3703,11 @@
       <c r="C5">
         <v>-4.9062499999999988E-2</v>
       </c>
+      <c r="D5">
+        <v>-4.7698632003669188E-2</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>0.3490658503988659</v>
       </c>
@@ -1923,8 +3717,11 @@
       <c r="C6">
         <v>-6.3073534200491652E-2</v>
       </c>
+      <c r="D6">
+        <v>-7.1203673875896642E-2</v>
+      </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>0.43633231299858238</v>
       </c>
@@ -1934,8 +3731,11 @@
       <c r="C7">
         <v>-7.516811098104971E-2</v>
       </c>
+      <c r="D7">
+        <v>-6.1565814782512031E-2</v>
+      </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>0.52359877559829882</v>
       </c>
@@ -1945,8 +3745,11 @@
       <c r="C8">
         <v>-8.4978742746348035E-2</v>
       </c>
+      <c r="D8">
+        <v>-6.1585023250091853E-2</v>
+      </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>0.6108652381980153</v>
       </c>
@@ -1956,8 +3759,11 @@
       <c r="C9">
         <v>-9.2207338414617243E-2</v>
       </c>
+      <c r="D9">
+        <v>-7.6357111013341666E-2</v>
+      </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>0.69813170079773179</v>
       </c>
@@ -1967,8 +3773,11 @@
       <c r="C10">
         <v>-9.6634260764322896E-2</v>
       </c>
+      <c r="D10">
+        <v>-7.0242739037592747E-2</v>
+      </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>0.78539816339744828</v>
       </c>
@@ -1978,8 +3787,11 @@
       <c r="C11">
         <v>-9.812499999999999E-2</v>
       </c>
+      <c r="D11">
+        <v>-7.2063441419449079E-2</v>
+      </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>0.87266462599716477</v>
       </c>
@@ -1989,8 +3801,11 @@
       <c r="C12">
         <v>-9.6634260764322896E-2</v>
       </c>
+      <c r="D12">
+        <v>-5.4431014025515964E-2</v>
+      </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>0.95993108859688125</v>
       </c>
@@ -2000,8 +3815,11 @@
       <c r="C13">
         <v>-9.2207338414617257E-2</v>
       </c>
+      <c r="D13">
+        <v>-6.3586025029903931E-2</v>
+      </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1.0471975511965976</v>
       </c>
@@ -2011,8 +3829,11 @@
       <c r="C14">
         <v>-8.4978742746348035E-2</v>
       </c>
+      <c r="D14">
+        <v>-6.9634672274783899E-2</v>
+      </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1.1344640137963142</v>
       </c>
@@ -2022,8 +3843,11 @@
       <c r="C15">
         <v>-7.516811098104971E-2</v>
       </c>
+      <c r="D15">
+        <v>-6.9121449390450146E-2</v>
+      </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1.2217304763960306</v>
       </c>
@@ -2033,8 +3857,11 @@
       <c r="C16">
         <v>-6.3073534200491679E-2</v>
       </c>
+      <c r="D16">
+        <v>-5.4767270689186465E-2</v>
+      </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1.3089969389957472</v>
       </c>
@@ -2044,8 +3871,11 @@
       <c r="C17">
         <v>-4.9062499999999988E-2</v>
       </c>
+      <c r="D17">
+        <v>-6.7734174317896106E-2</v>
+      </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1.3962634015954636</v>
       </c>
@@ -2055,8 +3885,11 @@
       <c r="C18">
         <v>-3.3560726563831259E-2</v>
       </c>
+      <c r="D18">
+        <v>-3.036914355966126E-2</v>
+      </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1.48352986419518</v>
       </c>
@@ -2066,8 +3899,11 @@
       <c r="C19">
         <v>-1.7039227433567575E-2</v>
       </c>
+      <c r="D19">
+        <v>-1.047889200553565E-2</v>
+      </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1.5707963267948966</v>
       </c>
@@ -2077,8 +3913,11 @@
       <c r="C20">
         <v>-1.2016846716633401E-17</v>
       </c>
+      <c r="D20">
+        <v>-8.6185038707664097E-5</v>
+      </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1.6580627893946129</v>
       </c>
@@ -2088,8 +3927,11 @@
       <c r="C21">
         <v>1.7039227433567505E-2</v>
       </c>
+      <c r="D21">
+        <v>1.0516091580590683E-2</v>
+      </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1.7453292519943295</v>
       </c>
@@ -2099,8 +3941,11 @@
       <c r="C22">
         <v>3.3560726563831231E-2</v>
       </c>
+      <c r="D22">
+        <v>3.0767640202002844E-2</v>
+      </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1.8325957145940459</v>
       </c>
@@ -2110,8 +3955,11 @@
       <c r="C23">
         <v>4.9062499999999974E-2</v>
       </c>
+      <c r="D23">
+        <v>6.8839772226522808E-2</v>
+      </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1.9198621771937625</v>
       </c>
@@ -2121,8 +3969,11 @@
       <c r="C24">
         <v>6.3073534200491652E-2</v>
       </c>
+      <c r="D24">
+        <v>5.3994415652076994E-2</v>
+      </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2.0071286397934789</v>
       </c>
@@ -2132,8 +3983,11 @@
       <c r="C25">
         <v>7.5168110981049696E-2</v>
       </c>
+      <c r="D25">
+        <v>6.9765887068951926E-2</v>
+      </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>2.0943951023931953</v>
       </c>
@@ -2143,8 +3997,11 @@
       <c r="C26">
         <v>8.4978742746348007E-2</v>
       </c>
+      <c r="D26">
+        <v>6.6843584513800139E-2</v>
+      </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>2.1816615649929116</v>
       </c>
@@ -2154,8 +4011,11 @@
       <c r="C27">
         <v>9.2207338414617229E-2</v>
       </c>
+      <c r="D27">
+        <v>6.2583274706921349E-2</v>
+      </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>2.2689280275926285</v>
       </c>
@@ -2165,8 +4025,11 @@
       <c r="C28">
         <v>9.6634260764322896E-2</v>
       </c>
+      <c r="D28">
+        <v>5.4549716300102309E-2</v>
+      </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>2.3561944901923448</v>
       </c>
@@ -2176,8 +4039,11 @@
       <c r="C29">
         <v>9.812499999999999E-2</v>
       </c>
+      <c r="D29">
+        <v>7.583773319791956E-2</v>
+      </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>2.4434609527920612</v>
       </c>
@@ -2187,8 +4053,11 @@
       <c r="C30">
         <v>9.663426076432291E-2</v>
       </c>
+      <c r="D30">
+        <v>7.0065438360958368E-2</v>
+      </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2.5307274153917776</v>
       </c>
@@ -2198,8 +4067,11 @@
       <c r="C31">
         <v>9.2207338414617271E-2</v>
       </c>
+      <c r="D31">
+        <v>8.0926870706645407E-2</v>
+      </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>2.6179938779914944</v>
       </c>
@@ -2209,8 +4081,11 @@
       <c r="C32">
         <v>8.4978742746348035E-2</v>
       </c>
+      <c r="D32">
+        <v>6.1786274525273813E-2</v>
+      </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2.7052603405912108</v>
       </c>
@@ -2220,8 +4095,11 @@
       <c r="C33">
         <v>7.5168110981049724E-2</v>
       </c>
+      <c r="D33">
+        <v>5.644731381453743E-2</v>
+      </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>2.7925268031909272</v>
       </c>
@@ -2231,8 +4109,11 @@
       <c r="C34">
         <v>6.3073534200491693E-2</v>
       </c>
+      <c r="D34">
+        <v>7.0555798178302695E-2</v>
+      </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2.8797932657906435</v>
       </c>
@@ -2242,8 +4123,11 @@
       <c r="C35">
         <v>4.9062500000000037E-2</v>
       </c>
+      <c r="D35">
+        <v>4.7012755730280992E-2</v>
+      </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>2.9670597283903599</v>
       </c>
@@ -2253,8 +4137,11 @@
       <c r="C36">
         <v>3.3560726563831307E-2</v>
       </c>
+      <c r="D36">
+        <v>4.9902252679533167E-2</v>
+      </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>3.0543261909900767</v>
       </c>
@@ -2264,8 +4151,11 @@
       <c r="C37">
         <v>1.7039227433567544E-2</v>
       </c>
+      <c r="D37">
+        <v>3.5444694990053066E-2</v>
+      </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>3.1415926535897931</v>
       </c>
@@ -2274,6 +4164,9 @@
       </c>
       <c r="C38">
         <v>2.4033693433266803E-17</v>
+      </c>
+      <c r="D38">
+        <v>-2.423451475907269E-4</v>
       </c>
     </row>
   </sheetData>
